--- a/EXAM_FORM1_RESULTS/EXAM_FORM1_61992.xlsx
+++ b/EXAM_FORM1_RESULTS/EXAM_FORM1_61992.xlsx
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>10</v>
+        <v>101</v>
       </c>
     </row>
     <row r="10">
@@ -548,7 +548,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Iviuic irl i</t>
+          <t>T</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>PLOLUSISLILE IIRL</t>
+          <t>IÊ</t>
         </is>
       </c>
     </row>
@@ -582,7 +582,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>G04H</t>
+          <t>G94D</t>
         </is>
       </c>
     </row>
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>61292</v>
+        <v>61992</v>
       </c>
     </row>
     <row r="18">

--- a/EXAM_FORM1_RESULTS/EXAM_FORM1_61992.xlsx
+++ b/EXAM_FORM1_RESULTS/EXAM_FORM1_61992.xlsx
@@ -453,7 +453,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>17/11/2025</t>
         </is>
       </c>
     </row>
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>101</v>
+        <v>110</v>
       </c>
     </row>
     <row r="10">
@@ -582,7 +582,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>G94D</t>
+          <t>G44J</t>
         </is>
       </c>
     </row>
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/EXAM_FORM1_RESULTS/EXAM_FORM1_61992.xlsx
+++ b/EXAM_FORM1_RESULTS/EXAM_FORM1_61992.xlsx
@@ -706,7 +706,7 @@
         <v>375</v>
       </c>
       <c r="K4" t="n">
-        <v>1001</v>
+        <v>4001</v>
       </c>
     </row>
     <row r="5">
@@ -733,7 +733,7 @@
         <v>14.8</v>
       </c>
       <c r="K7" t="n">
-        <v>121</v>
+        <v>101</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>

--- a/EXAM_FORM1_RESULTS/EXAM_FORM1_61992.xlsx
+++ b/EXAM_FORM1_RESULTS/EXAM_FORM1_61992.xlsx
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>110</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -706,7 +706,7 @@
         <v>375</v>
       </c>
       <c r="K4" t="n">
-        <v>4001</v>
+        <v>41</v>
       </c>
     </row>
     <row r="5">
@@ -733,7 +733,7 @@
         <v>14.8</v>
       </c>
       <c r="K7" t="n">
-        <v>101</v>
+        <v>10</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
